--- a/downloads/assets_data.xlsx
+++ b/downloads/assets_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>title</t>
   </si>
@@ -34,10 +34,19 @@
     <t>save_time</t>
   </si>
   <si>
+    <t>file_path</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
     <t>Tile World Match</t>
   </si>
   <si>
     <t>ARCADE: Ultimate Vehicles Pack – Low Poly Cars</t>
+  </si>
+  <si>
+    <t>2D RPG Starter Kit - Complete Game Template</t>
   </si>
   <si>
     <t>Item Description
@@ -90,6 +99,12 @@
 灰尘和雪粒</t>
   </si>
   <si>
+    <t>The Complete 2D RPG Kit – A 2D RPG Starter Kit In a Box!
+This template starter kit gives you a huge head start on making your very own 2D top-down RPG game complete with player movement (using the new input system), simple enemy behavior, level loading through portals, damage, health, weapon switching, menu system, tilemap level creation, coin pickups, and more.
+This template was designed to be beginner friendly and easy to understand, with all code fully commented and well spaced.
+In addition to the asset, there is also a detailed video tutorial series that walks you through how the template works in detail, and how to expand on it to add your own content. It’s everything you need to make an awesome 2D RPG!</t>
+  </si>
+  <si>
     <t>downloads\Tile_World_Match\thumbnail.webp</t>
   </si>
   <si>
@@ -100,6 +115,9 @@
   </si>
   <si>
     <t>https://unityassets4free.com/arcade-ultimate-vehicles-pack-low-poly-cars/</t>
+  </si>
+  <si>
+    <t>https://unityassets4free.com/2d-rpg-starter-kit-complete-game-template/</t>
   </si>
   <si>
     <t>2025-01-01 21:22:44</t>
@@ -476,10 +494,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,51 +516,72 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
-        <v>17</v>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/downloads/assets_data.xlsx
+++ b/downloads/assets_data.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="18517" windowHeight="8160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>title</t>
   </si>
@@ -37,16 +37,10 @@
     <t>file_path</t>
   </si>
   <si>
-    <t>content</t>
+    <t>file_name</t>
   </si>
   <si>
     <t>Tile World Match</t>
-  </si>
-  <si>
-    <t>ARCADE: Ultimate Vehicles Pack – Low Poly Cars</t>
-  </si>
-  <si>
-    <t>2D RPG Starter Kit - Complete Game Template</t>
   </si>
   <si>
     <t>Item Description
@@ -59,6 +53,30 @@
 – The faster the puzzle, the faster the 3 puzzle pieces, the more stars you will gain.
 – Collect enough stars and receive free gifts.
 – You can play Tile World – Puzzle Master anywhere, whether on your phone or on your tablet.</t>
+  </si>
+  <si>
+    <t>项目描述
+Tile World是一款结合了简单的麻将拼图和水果比赛的游戏，具有挑战性，但同样有趣。
+玩法说明
+–触摸，将三个拼图片放下框架。 组合三个相同的拼图将使它们从框架中消失并积累金币。
+–许多具有挑战性的关卡正在等着您。
+–只有当您吃掉关卡中的所有棋子时，您才能获胜。
+–以下关卡会有更高的挑战，更难的拼图。
+– The f 拼图越多， 3块拼图的速度越快，获得的星星就越多。
+–收集足够的星星并获得免费礼物。
+–您可以在任何地方玩Tile World – Puzzle Master ，无论是在手机还是平板电脑上。</t>
+  </si>
+  <si>
+    <t>downloads\Tile_World_Match\thumbnail.webp</t>
+  </si>
+  <si>
+    <t>https://unityassets4free.com/tile-world-match/</t>
+  </si>
+  <si>
+    <t>2025-01-01 21:22:44</t>
+  </si>
+  <si>
+    <t>ARCADE: Ultimate Vehicles Pack – Low Poly Cars</t>
   </si>
   <si>
     <t>A huge set of beautiful environment models all made in a distinctive geometric polygonal art style. Designed to make your game stand out from the crowd.
@@ -74,18 +92,6 @@
 Dust and Snow particles</t>
   </si>
   <si>
-    <t>项目描述
-Tile World是一款结合了简单的麻将拼图和水果比赛的游戏，具有挑战性，但同样有趣。
-玩法说明
-–触摸，将三个拼图片放下框架。 组合三个相同的拼图将使它们从框架中消失并积累金币。
-–许多具有挑战性的关卡正在等着您。
-–只有当您吃掉关卡中的所有棋子时，您才能获胜。
-–以下关卡会有更高的挑战，更难的拼图。
-– The f 拼图越多， 3块拼图的速度越快，获得的星星就越多。
-–收集足够的星星并获得免费礼物。
-–您可以在任何地方玩Tile World – Puzzle Master ，无论是在手机还是平板电脑上。</t>
-  </si>
-  <si>
     <t>一大批美丽的环境模型，均采用独特的几何多边形艺术风格。 旨在让您的游戏在人群中脱颖而出。
 超过90个预制件，所有预制件都设置了碰撞，并准备好放入场景中。
 展示夏季、冬季和沙漠环境的3个独立示例场景。
@@ -99,51 +105,69 @@
 灰尘和雪粒</t>
   </si>
   <si>
+    <t>downloads\ARCADE__Ultimate_Vehicles_Pack_–_Low_Poly_Cars\thumbnail.jpg</t>
+  </si>
+  <si>
+    <t>https://unityassets4free.com/arcade-ultimate-vehicles-pack-low-poly-cars/</t>
+  </si>
+  <si>
+    <t>2025-01-01 21:22:55</t>
+  </si>
+  <si>
+    <t>2D RPG Starter Kit - Complete Game Template</t>
+  </si>
+  <si>
     <t>The Complete 2D RPG Kit – A 2D RPG Starter Kit In a Box!
 This template starter kit gives you a huge head start on making your very own 2D top-down RPG game complete with player movement (using the new input system), simple enemy behavior, level loading through portals, damage, health, weapon switching, menu system, tilemap level creation, coin pickups, and more.
 This template was designed to be beginner friendly and easy to understand, with all code fully commented and well spaced.
 In addition to the asset, there is also a detailed video tutorial series that walks you through how the template works in detail, and how to expand on it to add your own content. It’s everything you need to make an awesome 2D RPG!</t>
   </si>
   <si>
-    <t>downloads\Tile_World_Match\thumbnail.webp</t>
-  </si>
-  <si>
-    <t>downloads\ARCADE__Ultimate_Vehicles_Pack_–_Low_Poly_Cars\thumbnail.jpg</t>
-  </si>
-  <si>
-    <t>https://unityassets4free.com/tile-world-match/</t>
-  </si>
-  <si>
-    <t>https://unityassets4free.com/arcade-ultimate-vehicles-pack-low-poly-cars/</t>
-  </si>
-  <si>
     <t>https://unityassets4free.com/2d-rpg-starter-kit-complete-game-template/</t>
   </si>
   <si>
-    <t>2025-01-01 21:22:44</t>
-  </si>
-  <si>
-    <t>2025-01-01 21:22:55</t>
+    <t>完整的2D RPG套件–盒装2D RPG入门套件！
+这个模板入门套件让您在制作自己的2D自上而下的RPG游戏方面有一个巨大的开端，包括玩家移动（使用新的输入系统）、简单的敌人行为、通过门户加载关卡、伤害、生命值、武器切换、菜单系统、瓦片地图关卡创建、硬币拾取等。
+此模板专为初学者设计，易于理解，所有代码均有完整注释，间距也很宽。
+此外， t 在资源方面，还有一个详细的视频教程系列，引导您详细了解模板的工作原理，以及如何对其进行扩展以添加自己的内容。制作精彩的2D RPG所需的一切！</t>
+  </si>
+  <si>
+    <t>E:\Proj\AI\taobao\downloads\2D_RPG_Starter_Kit_-_Complete_Game_Template\thumbnail.webp</t>
+  </si>
+  <si>
+    <t>2025-01-02 00:45:58</t>
+  </si>
+  <si>
+    <t>F:\0游戏教程\0tele\2D RPG topdown MEGA BUNDLE v2.0.0.unitypackage</t>
+  </si>
+  <si>
+    <t>2D_RPG_Starter_Kit_-_Complete_Game_Template</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -151,18 +175,347 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -185,12 +538,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
@@ -198,14 +790,65 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="10" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -488,14 +1131,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
@@ -523,66 +1166,91 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" ht="14.25" spans="1:6">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" ht="14.25" spans="1:6">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="4" ht="14.25" spans="1:5">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
+    <row r="5" ht="14.25" spans="1:8">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="H4" t="s">
-        <v>15</v>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E2" r:id="rId1" display="https://unityassets4free.com/tile-world-match/"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://unityassets4free.com/arcade-ultimate-vehicles-pack-low-poly-cars/"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://unityassets4free.com/2d-rpg-starter-kit-complete-game-template/"/>
+    <hyperlink ref="E5" r:id="rId3" display="https://unityassets4free.com/2d-rpg-starter-kit-complete-game-template/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>